--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T14:16:19+00:00</t>
+    <t>2025-02-13T08:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:25:30+00:00</t>
+    <t>2025-02-13T08:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:54:32+00:00</t>
+    <t>2025-02-14T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -916,10 +916,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>This identifies the vital sign result type.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-vitalparameterarten</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -2020,7 +2017,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.67578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5361,11 +5358,9 @@
       <c r="X28" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5398,30 +5393,30 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5444,19 +5439,19 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5505,7 +5500,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5520,19 +5515,19 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5540,10 +5535,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5566,16 +5561,16 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5625,7 +5620,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5646,13 +5641,13 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5660,14 +5655,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5686,19 +5681,19 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5747,7 +5742,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5762,19 +5757,19 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5782,14 +5777,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5808,19 +5803,19 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5869,7 +5864,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5878,25 +5873,25 @@
         <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AJ32" t="s" s="2">
+      <c r="AK32" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5904,10 +5899,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5930,16 +5925,16 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5989,7 +5984,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6010,13 +6005,13 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6024,10 +6019,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6050,17 +6045,17 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6109,7 +6104,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6124,19 +6119,19 @@
         <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6144,10 +6139,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6170,19 +6165,19 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6231,7 +6226,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6240,7 +6235,7 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>104</v>
@@ -6249,27 +6244,27 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>364</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6295,16 +6290,16 @@
         <v>189</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6332,11 +6327,11 @@
         <v>289</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6353,7 +6348,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6362,7 +6357,7 @@
         <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6377,7 +6372,7 @@
         <v>135</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6388,14 +6383,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6417,16 +6412,16 @@
         <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6454,11 +6449,11 @@
         <v>289</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6475,7 +6470,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6493,27 +6488,27 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6536,19 +6531,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6597,7 +6592,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6618,10 +6613,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6632,10 +6627,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6661,13 +6656,13 @@
         <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6693,14 +6688,14 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6717,7 +6712,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6735,27 +6730,27 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6781,16 +6776,16 @@
         <v>189</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6815,14 +6810,14 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6839,7 +6834,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6860,10 +6855,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6874,10 +6869,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6900,16 +6895,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6959,7 +6954,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6977,27 +6972,27 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7020,16 +7015,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7079,7 +7074,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7097,27 +7092,27 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7140,19 +7135,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7201,7 +7196,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7213,19 +7208,19 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7236,10 +7231,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7354,10 +7349,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7474,14 +7469,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7503,10 +7498,10 @@
         <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>141</v>
@@ -7561,7 +7556,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7596,10 +7591,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7622,13 +7617,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7679,7 +7674,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7688,7 +7683,7 @@
         <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>104</v>
@@ -7700,10 +7695,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7714,10 +7709,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7740,13 +7735,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7797,7 +7792,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7806,7 +7801,7 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
@@ -7818,10 +7813,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7832,10 +7827,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7861,16 +7856,16 @@
         <v>189</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7898,11 +7893,11 @@
         <v>116</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7919,7 +7914,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7937,13 +7932,13 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7954,10 +7949,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7983,16 +7978,16 @@
         <v>189</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8017,14 +8012,14 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>474</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8041,7 +8036,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8059,13 +8054,13 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AN50" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8076,10 +8071,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8102,17 +8097,17 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8161,7 +8156,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8185,7 +8180,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8196,10 +8191,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8225,10 +8220,10 @@
         <v>204</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8279,7 +8274,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8300,10 +8295,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8314,10 +8309,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8340,16 +8335,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8399,7 +8394,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8420,10 +8415,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8434,10 +8429,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8460,16 +8455,16 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8519,7 +8514,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8540,10 +8535,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8554,10 +8549,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8580,19 +8575,19 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8641,7 +8636,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8653,19 +8648,19 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8676,10 +8671,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8794,10 +8789,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8914,14 +8909,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8943,10 +8938,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>141</v>
@@ -9001,7 +8996,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9036,10 +9031,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9065,16 +9060,16 @@
         <v>189</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9101,12 +9096,10 @@
       <c r="X59" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Y59" s="2"/>
+      <c r="Z59" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9123,7 +9116,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>92</v>
@@ -9141,16 +9134,16 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9158,10 +9151,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9184,19 +9177,19 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="N60" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="O60" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9224,11 +9217,11 @@
         <v>289</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9245,7 +9238,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9254,7 +9247,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9263,27 +9256,27 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>364</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9309,16 +9302,16 @@
         <v>189</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N61" t="s" s="2">
-        <v>525</v>
-      </c>
       <c r="O61" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9346,11 +9339,11 @@
         <v>289</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9367,7 +9360,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9376,7 +9369,7 @@
         <v>92</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>104</v>
@@ -9391,7 +9384,7 @@
         <v>135</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9402,14 +9395,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9431,16 +9424,16 @@
         <v>189</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9468,11 +9461,11 @@
         <v>289</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9489,7 +9482,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9507,27 +9500,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9553,16 +9546,16 @@
         <v>83</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>530</v>
-      </c>
       <c r="N63" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9611,7 +9604,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9632,10 +9625,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T08:32:04+00:00</t>
+    <t>2025-02-14T09:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationvitalsigns.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -916,7 +916,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-vitalparameterarten</t>
+    <t>This identifies the vital sign result type.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -2017,7 +2020,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.67578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5358,9 +5361,11 @@
       <c r="X28" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Y28" s="2"/>
+      <c r="Y28" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5393,30 +5398,30 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5439,19 +5444,19 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5500,7 +5505,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5515,19 +5520,19 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5535,10 +5540,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5561,16 +5566,16 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5620,7 +5625,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5641,13 +5646,13 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5655,14 +5660,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5681,19 +5686,19 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5742,7 +5747,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5757,19 +5762,19 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5777,14 +5782,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5803,19 +5808,19 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5864,7 +5869,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5873,25 +5878,25 @@
         <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5899,10 +5904,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5925,16 +5930,16 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5984,7 +5989,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6005,13 +6010,13 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6019,10 +6024,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6045,17 +6050,17 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6104,7 +6109,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6119,19 +6124,19 @@
         <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6139,10 +6144,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6165,19 +6170,19 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6226,7 +6231,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6235,7 +6240,7 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>104</v>
@@ -6244,27 +6249,27 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6290,16 +6295,16 @@
         <v>189</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6327,10 +6332,10 @@
         <v>289</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6348,7 +6353,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6357,7 +6362,7 @@
         <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6372,7 +6377,7 @@
         <v>135</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6383,14 +6388,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6412,16 +6417,16 @@
         <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6449,10 +6454,10 @@
         <v>289</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6470,7 +6475,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6488,27 +6493,27 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6531,19 +6536,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6592,7 +6597,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6613,10 +6618,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6627,10 +6632,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6656,13 +6661,13 @@
         <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6688,13 +6693,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6712,7 +6717,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6730,27 +6735,27 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6776,16 +6781,16 @@
         <v>189</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6810,13 +6815,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6834,7 +6839,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6855,10 +6860,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6869,10 +6874,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6895,16 +6900,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6954,7 +6959,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6972,27 +6977,27 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7015,16 +7020,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7074,7 +7079,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7092,27 +7097,27 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7135,19 +7140,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7196,7 +7201,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7208,7 +7213,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7217,10 +7222,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7231,10 +7236,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7349,10 +7354,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7469,14 +7474,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7498,10 +7503,10 @@
         <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>141</v>
@@ -7556,7 +7561,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7591,10 +7596,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7617,13 +7622,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7674,7 +7679,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7683,7 +7688,7 @@
         <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>104</v>
@@ -7695,10 +7700,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7709,10 +7714,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7735,13 +7740,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7792,7 +7797,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7801,7 +7806,7 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
@@ -7813,10 +7818,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7827,10 +7832,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7856,16 +7861,16 @@
         <v>189</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7893,10 +7898,10 @@
         <v>116</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7914,7 +7919,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7932,13 +7937,13 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7949,10 +7954,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7978,16 +7983,16 @@
         <v>189</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8012,13 +8017,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8036,7 +8041,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8054,13 +8059,13 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8071,10 +8076,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8097,17 +8102,17 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8156,7 +8161,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8180,7 +8185,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8191,10 +8196,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8220,10 +8225,10 @@
         <v>204</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8274,7 +8279,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8295,10 +8300,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8309,10 +8314,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8335,16 +8340,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8394,7 +8399,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8415,10 +8420,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8429,10 +8434,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8455,16 +8460,16 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8514,7 +8519,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8535,10 +8540,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8549,10 +8554,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8575,19 +8580,19 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8636,7 +8641,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8648,7 +8653,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8657,10 +8662,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8671,10 +8676,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8789,10 +8794,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8909,14 +8914,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8938,10 +8943,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>141</v>
@@ -8996,7 +9001,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9031,10 +9036,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9060,16 +9065,16 @@
         <v>189</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9096,9 +9101,11 @@
       <c r="X59" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Y59" s="2"/>
+      <c r="Y59" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9116,7 +9123,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>92</v>
@@ -9134,16 +9141,16 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9151,10 +9158,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9177,19 +9184,19 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9217,10 +9224,10 @@
         <v>289</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9238,7 +9245,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9247,7 +9254,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9256,27 +9263,27 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9302,16 +9309,16 @@
         <v>189</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9339,10 +9346,10 @@
         <v>289</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9360,7 +9367,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9369,7 +9376,7 @@
         <v>92</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>104</v>
@@ -9384,7 +9391,7 @@
         <v>135</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9395,14 +9402,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9424,16 +9431,16 @@
         <v>189</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9461,10 +9468,10 @@
         <v>289</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9482,7 +9489,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9500,27 +9507,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9546,16 +9553,16 @@
         <v>83</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9604,7 +9611,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9625,10 +9632,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
